--- a/PMA.xlsx
+++ b/PMA.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>46</t>
         </is>
       </c>
     </row>

--- a/PMA.xlsx
+++ b/PMA.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VV</t>
+          <t>VM-D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>230</t>
         </is>
       </c>
     </row>

--- a/PMA.xlsx
+++ b/PMA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,21 @@
           <t>Tensión [kV]</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Corriente nominal [A]</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clase de tensión [kV]</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VM-D</t>
+          <t>RMV-II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,8 +456,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>230</t>
-        </is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
